--- a/data/trans_orig/IQ3006_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3006_MoAR-Habitat-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en años en la que empezaron a beber leche normal</t>
+          <t>Menores según la edad en años en la que empezaron a beber leche normal (tasa de respuesta: 32,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,69; 14,66</t>
+          <t>8,11; 14,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,0; 14,69</t>
+          <t>12,03; 14,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,32 +692,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,18; 15,34</t>
+          <t>12,16; 15,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,52; 16,86</t>
+          <t>13,3; 16,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,21; 17,88</t>
+          <t>12,16; 17,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,57; 14,6</t>
+          <t>11,53; 14,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,08; 15,53</t>
+          <t>13,15; 15,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,2; 16,72</t>
+          <t>12,39; 16,83</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,09; 15,33</t>
+          <t>9,59; 15,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,62; 14,62</t>
+          <t>11,56; 14,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,34; 15,59</t>
+          <t>10,6; 15,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,43; 13,86</t>
+          <t>10,45; 13,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,28; 15,68</t>
+          <t>9,92; 15,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,05; 14,23</t>
+          <t>9,12; 13,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,61; 13,77</t>
+          <t>10,81; 13,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,44; 14,37</t>
+          <t>11,4; 14,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,24; 13,86</t>
+          <t>10,27; 13,91</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,94; 21,41</t>
+          <t>14,92; 21,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,8; 17,35</t>
+          <t>11,47; 17,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,5; 17,23</t>
+          <t>10,48; 17,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,51; 15,38</t>
+          <t>10,56; 16,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 12,69</t>
+          <t>6,4; 12,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,0; 13,03</t>
+          <t>11,0; 13,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,31; 16,98</t>
+          <t>12,21; 16,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,14; 14,93</t>
+          <t>10,4; 14,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,26; 13,95</t>
+          <t>11,22; 13,95</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,48; 15,39</t>
+          <t>11,49; 15,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,49; 17,01</t>
+          <t>12,53; 16,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,7; 15,53</t>
+          <t>11,59; 15,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 14,14</t>
+          <t>10,1; 14,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,3; 16,13</t>
+          <t>12,3; 16,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,07; 17,09</t>
+          <t>9,23; 17,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,16; 14,21</t>
+          <t>11,26; 14,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,87; 15,88</t>
+          <t>12,91; 15,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,29; 14,91</t>
+          <t>11,49; 15,1</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,06; 15,01</t>
+          <t>11,97; 14,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,82; 14,89</t>
+          <t>12,79; 14,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,69; 14,33</t>
+          <t>11,92; 14,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,5; 13,45</t>
+          <t>11,4; 13,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,18; 14,75</t>
+          <t>12,17; 14,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,18; 13,89</t>
+          <t>11,23; 13,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,06; 13,73</t>
+          <t>12,09; 13,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,78; 14,37</t>
+          <t>12,9; 14,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,86; 13,65</t>
+          <t>11,85; 13,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3006_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3006_MoAR-Habitat-trans_orig.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,11; 14,87</t>
+          <t>8,61; 14,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,03; 14,7</t>
+          <t>12,09; 14,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,32 +692,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,16; 15,45</t>
+          <t>12,18; 15,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,3; 16,87</t>
+          <t>13,43; 16,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,16; 17,62</t>
+          <t>11,84; 17,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,53; 14,56</t>
+          <t>11,45; 14,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,15; 15,5</t>
+          <t>13,06; 15,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,39; 16,83</t>
+          <t>12,36; 16,82</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,59; 15,36</t>
+          <t>9,49; 15,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,56; 14,54</t>
+          <t>11,67; 14,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,6; 15,85</t>
+          <t>10,51; 15,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,45; 13,83</t>
+          <t>10,39; 13,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,92; 15,49</t>
+          <t>9,98; 15,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 13,98</t>
+          <t>9,07; 13,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,81; 13,93</t>
+          <t>10,73; 13,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,4; 14,45</t>
+          <t>11,42; 14,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,27; 13,91</t>
+          <t>10,41; 14,01</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,92; 21,36</t>
+          <t>14,97; 21,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,47; 17,27</t>
+          <t>11,5; 17,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,48; 17,09</t>
+          <t>10,59; 17,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,56; 16,42</t>
+          <t>10,62; 16,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 12,52</t>
+          <t>6,3; 12,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,0; 13,22</t>
+          <t>10,93; 13,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,21; 16,85</t>
+          <t>12,29; 16,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,4; 14,86</t>
+          <t>10,22; 14,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,22; 13,95</t>
+          <t>11,32; 14,12</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,49; 15,5</t>
+          <t>11,31; 15,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,53; 16,85</t>
+          <t>12,55; 17,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,59; 15,33</t>
+          <t>11,58; 15,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,1; 14,24</t>
+          <t>9,92; 14,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,3; 16,24</t>
+          <t>12,35; 16,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 17,27</t>
+          <t>9,3; 17,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,26; 14,32</t>
+          <t>11,28; 14,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,91; 15,85</t>
+          <t>12,71; 15,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,49; 15,1</t>
+          <t>11,41; 15,25</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,97; 14,86</t>
+          <t>11,93; 14,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,79; 14,75</t>
+          <t>12,8; 14,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,92; 14,41</t>
+          <t>11,92; 14,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,4; 13,49</t>
+          <t>11,45; 13,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,17; 14,64</t>
+          <t>12,24; 14,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,23; 13,99</t>
+          <t>11,2; 13,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,09; 13,72</t>
+          <t>12,05; 13,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,9; 14,5</t>
+          <t>12,8; 14,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,85; 13,72</t>
+          <t>11,91; 13,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3006_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3006_MoAR-Habitat-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13,73</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15,13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14,56</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>12,27</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>13,0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>13,16</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,73</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,13</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,56</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,61; 14,66</t>
+          <t>12,18; 15,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,09; 14,64</t>
+          <t>13,52; 16,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>12,21; 17,88</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8,69; 14,66</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>12,0; 14,69</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>12,0; 16,48</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12,18; 15,54</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13,43; 16,82</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11,84; 17,77</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,45; 14,55</t>
+          <t>11,57; 14,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,06; 15,58</t>
+          <t>13,08; 15,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,36; 16,82</t>
+          <t>12,2; 16,72</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12,22</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13,13</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11,2</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>12,41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>13,07</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>12,67</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,22</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,13</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,2</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,49; 15,47</t>
+          <t>10,43; 13,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,67; 14,62</t>
+          <t>10,28; 15,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,51; 15,82</t>
+          <t>9,05; 14,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,39; 13,99</t>
+          <t>9,09; 15,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,98; 15,27</t>
+          <t>11,62; 14,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,07; 13,88</t>
+          <t>10,34; 15,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,73; 13,9</t>
+          <t>10,61; 13,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,42; 14,34</t>
+          <t>11,44; 14,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10,41; 14,01</t>
+          <t>10,24; 13,86</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12,12</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,84</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,87</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>18,64</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>14,57</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>13,48</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,12</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,84</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,87</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,97; 21,36</t>
+          <t>10,51; 15,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,5; 17,2</t>
+          <t>6,49; 12,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,59; 17,13</t>
+          <t>11,0; 13,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,62; 16,07</t>
+          <t>14,94; 21,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,52</t>
+          <t>11,8; 17,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,93; 13,07</t>
+          <t>10,5; 17,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,29; 16,9</t>
+          <t>12,31; 16,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,22; 14,86</t>
+          <t>10,14; 14,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,32; 14,12</t>
+          <t>11,26; 13,95</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,08</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,99</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,72</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>13,45</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>14,18</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,26</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,08</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,99</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,72</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,31; 15,47</t>
+          <t>10,03; 14,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,55; 17,12</t>
+          <t>12,3; 16,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,58; 15,2</t>
+          <t>9,07; 17,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,92; 14,22</t>
+          <t>11,48; 15,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,35; 16,23</t>
+          <t>12,49; 17,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,3; 17,1</t>
+          <t>11,7; 15,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,28; 14,25</t>
+          <t>11,16; 14,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,71; 15,72</t>
+          <t>12,87; 15,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,41; 15,25</t>
+          <t>11,29; 14,91</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,48</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13,5</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12,51</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>13,47</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>13,68</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>13,1</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12,48</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,5</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,51</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,93; 14,9</t>
+          <t>11,5; 13,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,8; 14,81</t>
+          <t>12,18; 14,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,92; 14,53</t>
+          <t>11,18; 13,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,45; 13,46</t>
+          <t>12,06; 15,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,24; 14,58</t>
+          <t>12,82; 14,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,97</t>
+          <t>11,69; 14,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,05; 13,72</t>
+          <t>12,06; 13,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,8; 14,39</t>
+          <t>12,78; 14,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,91; 13,83</t>
+          <t>11,86; 13,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3006_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3006_MoAR-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en años en la que empezaron a beber leche normal (tasa de respuesta: 32,45%)</t>
+          <t>Edad media en meses a la que los menores empezaron a beber leche normal (tasa de respuesta: 32,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>13,73</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15,13</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14,56</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,27</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,16</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>14,23</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14,22</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>13.73231878327677</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>15.13365438915261</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>14.55897661996014</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>12.26961141253812</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>12.99711462274465</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>13.15721881566647</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>13.19998581973026</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>14.23150566678171</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>14.21777828373097</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>12,18; 15,34</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13,52; 16,86</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12,21; 17,88</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8,69; 14,66</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12,0; 14,69</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,0; 16,48</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,57; 14,6</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13,08; 15,53</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12,2; 16,72</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>12.18485438854353</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>13.52270767607229</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>12.20871313208398</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>8.690522470493312</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>11.5676645284211</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>13.08499204256647</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>12.19867408995706</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>15.34281730321526</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>16.8634735330621</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>17.88140035462269</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>14.65957345065319</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>14.69266420958613</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>16.47905234649592</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>14.60419933763686</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>15.52699655086292</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>16.71751259199685</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>12,22</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13,13</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11,2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12,41</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,07</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,67</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>12,29</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>13,1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>11,9</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>10,43; 13,86</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10,28; 15,68</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9,05; 14,23</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9,09; 15,33</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11,62; 14,62</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10,34; 15,59</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,61; 13,77</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11,44; 14,37</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10,24; 13,86</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>12.21752809210637</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>13.13164221668675</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>11.20427602346736</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>12.40710020749137</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>13.07031987238823</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>12.66674680275056</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>12.29013937396509</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>13.09880782160938</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>11.89805665557857</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>12,12</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9,84</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>11,87</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18,64</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,57</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,48</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,27</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>12,65</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>12,41</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>10.43364957250722</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>10.28010585287291</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>9.053290768471898</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>9.088544147439004</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>11.6179230883587</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>10.34132663074856</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>10.60863831923163</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>11.43507251226389</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>10.24166139218562</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>10,51; 15,38</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>6,49; 12,69</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>11,0; 13,03</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>14,94; 21,41</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>11,8; 17,35</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>10,5; 17,23</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>12,31; 16,98</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>10,14; 14,93</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>11,26; 13,95</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>13.86171725321012</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>15.67840399352946</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>14.22674937267499</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>15.32564648327302</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>14.62083485516126</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>15.58690083613696</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>13.76681436383248</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>14.37459509113271</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>13.85972133448998</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,217 +845,324 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>12,08</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>13,99</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12,72</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13,45</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,18</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,26</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,77</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14,1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>13,09</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>12.12477809624545</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>9.839505966730783</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>11.87490733435948</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>18.64358293393532</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>14.56583074332455</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>13.48459582962817</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>14.26961126038352</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>12.65216252090765</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>12.41355973972583</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>10,03; 14,14</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>12,3; 16,13</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9,07; 17,09</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11,48; 15,39</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12,49; 17,01</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11,7; 15,53</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>11,16; 14,21</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>12,87; 15,88</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>11,29; 14,91</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>10.51306362111489</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>6.488727692222785</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>11.00376994187637</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>14.93954236707418</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>11.80190992367473</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>10.49809348188558</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>12.30852244310968</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>10.14453387564427</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>11.26280839953113</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>15.37702994405936</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>12.68731211855871</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>13.03322631834361</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>21.40763124033099</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>17.34612996344738</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>17.23326177997098</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>16.98368530346879</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>14.93269431289364</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>13.94670637419963</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>12.08122738644657</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>13.98759986469701</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>12.71641524859398</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>13.45398839495981</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>14.18244036345063</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>13.25926111360487</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>12.77499897632975</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>14.09612491805205</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>13.08678121256325</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>10.02941883397586</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>12.29733741102191</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>9.067023526115744</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>11.47750363466208</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>12.49048541182037</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>11.69972088784296</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>11.15613728340171</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>12.86769852603075</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>11.29444761260456</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>14.13696126976509</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>16.13349286597992</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>17.09133270883229</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>15.38817043715784</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>17.01456320398245</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>15.52527735989617</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>14.20870716533165</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>15.88288660870669</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>14.91286861438695</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>12,48</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>13,5</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12,51</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13,47</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,68</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>13,1</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,89</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13,6</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12,79</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>11,5; 13,45</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12,18; 14,75</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11,18; 13,89</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12,06; 15,01</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>12,82; 14,89</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,69; 14,33</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,06; 13,73</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12,78; 14,37</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11,86; 13,65</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>12.47940148167789</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>13.49924036577606</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>12.50837994312027</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>13.46861685162289</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>13.68314837747166</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>13.09862053076608</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>12.89211955043876</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>13.59600984365392</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>12.78585706280553</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>11.50193427217702</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>12.18039721621262</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>11.18194501399569</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>12.06133895234819</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>12.81889711434753</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>11.69357633633587</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>12.06281986747988</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>12.77502136732149</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>11.85601471548406</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>13.45410959575876</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>14.74564290196101</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>13.88503730545816</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>15.0127250221112</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>14.8948749878188</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>14.32679585078538</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>13.73021332953642</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>14.37143749666116</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>13.65093586345517</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1171,14 +1171,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
